--- a/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
@@ -379,6 +379,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>

--- a/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -790,7 +791,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -812,7 +812,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -841,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -916,7 +914,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -942,7 +940,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -968,7 +966,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -994,7 +992,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1020,7 +1018,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -791,6 +790,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -812,6 +812,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -840,6 +841,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -914,7 +916,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -940,7 +942,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -966,7 +968,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -992,7 +994,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1018,7 +1020,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -156,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Jamaica power generation by type (MSET / JPS, annual) (to 2025)</a:t>
             </a:r>
           </a:p>
@@ -790,7 +792,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -812,7 +813,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -841,7 +841,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -916,7 +915,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -942,7 +941,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -968,7 +967,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -994,7 +993,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1020,7 +1019,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/jamaica_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -792,6 +791,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -813,6 +813,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -841,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -915,7 +917,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -941,7 +943,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -967,7 +969,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -993,7 +995,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1019,7 +1021,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">
